--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562487553</v>
+        <v>46157.93071686848</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071686848</v>
+        <v>46157.93155191235</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93155191235</v>
+        <v>46157.93394188586</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394188586</v>
+        <v>46157.93709451714</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709451714</v>
+        <v>46158.28211105647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211105647</v>
+        <v>46158.29666498338</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666498338</v>
+        <v>46158.2980615314</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980615314</v>
+        <v>46158.33381901361</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381901361</v>
+        <v>46158.36848638592</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36848638592</v>
+        <v>46158.37282067558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
